--- a/artfynd/A 62568-2025 artfynd.xlsx
+++ b/artfynd/A 62568-2025 artfynd.xlsx
@@ -675,45 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133083620</v>
+        <v>133083611</v>
       </c>
       <c r="B2" t="n">
-        <v>91891</v>
+        <v>89354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kårebolsätern, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>414268</v>
+        <v>414241</v>
       </c>
       <c r="R2" t="n">
-        <v>6697588</v>
+        <v>6697575</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -746,6 +757,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Tydlig doft av Kokkos eller ev. kemisk.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,56 +788,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133083611</v>
+        <v>133083553</v>
       </c>
       <c r="B3" t="n">
-        <v>89310</v>
+        <v>91937</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kårebolsätern, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>414241</v>
+        <v>413874</v>
       </c>
       <c r="R3" t="n">
-        <v>6697575</v>
+        <v>6697323</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -856,17 +861,13 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Tydlig doft av Kokkos eller ev. kemisk.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -878,17 +879,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joakim Karlsson, Svenja Neeb, Ossian Fjordefalk</t>
+          <t>Joakim Karlsson, Ossian Fjordefalk, Svenja Neeb</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133083553</v>
+        <v>133083620</v>
       </c>
       <c r="B4" t="n">
-        <v>91891</v>
+        <v>91937</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>413874</v>
+        <v>414268</v>
       </c>
       <c r="R4" t="n">
-        <v>6697323</v>
+        <v>6697588</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -964,7 +965,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -976,7 +976,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joakim Karlsson, Ossian Fjordefalk, Svenja Neeb</t>
+          <t>Joakim Karlsson, Svenja Neeb, Ossian Fjordefalk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 62568-2025 artfynd.xlsx
+++ b/artfynd/A 62568-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -981,6 +981,112 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135401958</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58812</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sjöbäckåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>413673</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6697211</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62568-2025 artfynd.xlsx
+++ b/artfynd/A 62568-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133083611</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133083553</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133083620</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,8 +1106,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135401958</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 62568-2025 artfynd.xlsx
+++ b/artfynd/A 62568-2025 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>135401958</v>
       </c>
       <c r="B5" t="n">
-        <v>58812</v>
+        <v>58817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62568-2025 artfynd.xlsx
+++ b/artfynd/A 62568-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -998,6 +998,117 @@
       <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/133083620</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135401958</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sjöbäckåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>413673</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6697211</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135401958</t>
         </is>
       </c>
     </row>
@@ -1006,6 +1117,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62568-2025 artfynd.xlsx
+++ b/artfynd/A 62568-2025 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>135401958</v>
       </c>
       <c r="B5" t="n">
-        <v>58817</v>
+        <v>58819</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
